--- a/Assets/Resources/MasterData/CharacterData.xlsx
+++ b/Assets/Resources/MasterData/CharacterData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teacher\Documents\2DRoguelikeAlfa\Assets\Resources\MasterData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEED8CC9-4A57-447F-BD15-D681F6927450}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{233872E4-1133-45EA-BD92-CDD96E61AEDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -449,7 +449,7 @@
         <v>20</v>
       </c>
       <c r="E2" s="2">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="F2" s="2">
         <v>1</v>

--- a/Assets/Resources/MasterData/CharacterData.xlsx
+++ b/Assets/Resources/MasterData/CharacterData.xlsx
@@ -1,31 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teacher\Documents\2DRoguelikeAlfa\Assets\Resources\MasterData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{233872E4-1133-45EA-BD92-CDD96E61AEDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A7A7518-5D67-4267-AF5C-AE07462AE772}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2490" yWindow="-13950" windowWidth="12630" windowHeight="13725" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CharacterData" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1"/>
@@ -56,6 +65,18 @@
   </si>
   <si>
     <t>rogue_player_</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>rogue_sand_enemy2_</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>rogue_snow_enemy1_</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>rogue_urban_enemy1_</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -404,7 +425,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="3.375" bestFit="1" customWidth="1"/>
@@ -440,7 +461,8 @@
         <v>0</v>
       </c>
       <c r="B2" s="2">
-        <v>0</v>
+        <f>A2+10000</f>
+        <v>10000</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>7</v>
@@ -460,7 +482,8 @@
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>1</v>
+        <f t="shared" ref="B3:B6" si="0">A3+10000</f>
+        <v>10001</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>6</v>
@@ -472,6 +495,69 @@
         <v>2</v>
       </c>
       <c r="F3" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="2">
+        <v>2</v>
+      </c>
+      <c r="B4" s="2">
+        <f t="shared" si="0"/>
+        <v>10002</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="2">
+        <v>15</v>
+      </c>
+      <c r="E4" s="2">
+        <v>3</v>
+      </c>
+      <c r="F4" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="2">
+        <v>3</v>
+      </c>
+      <c r="B5" s="2">
+        <f t="shared" si="0"/>
+        <v>10003</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="2">
+        <v>20</v>
+      </c>
+      <c r="E5" s="2">
+        <v>4</v>
+      </c>
+      <c r="F5" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="2">
+        <v>4</v>
+      </c>
+      <c r="B6" s="2">
+        <f t="shared" si="0"/>
+        <v>10004</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" s="2">
+        <v>17</v>
+      </c>
+      <c r="E6" s="2">
+        <v>5</v>
+      </c>
+      <c r="F6" s="2">
         <v>1</v>
       </c>
     </row>

--- a/Assets/Resources/MasterData/CharacterData.xlsx
+++ b/Assets/Resources/MasterData/CharacterData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teacher\Documents\2DRoguelikeAlfa\Assets\Resources\MasterData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A7A7518-5D67-4267-AF5C-AE07462AE772}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9221C6D-5D28-4105-A347-86C1ADDBF3C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2490" yWindow="-13950" windowWidth="12630" windowHeight="13725" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="930" yWindow="-14610" windowWidth="16995" windowHeight="10170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CharacterData" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="12">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1"/>
@@ -77,6 +77,10 @@
   </si>
   <si>
     <t>rogue_urban_enemy1_</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ActionID[]</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -114,7 +118,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -137,14 +141,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -425,7 +441,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="3.375" bestFit="1" customWidth="1"/>
@@ -434,9 +450,10 @@
     <col min="4" max="4" width="4.125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="7" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="8.625" bestFit="1" customWidth="1"/>
+    <col min="7" max="10" width="10.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -455,8 +472,20 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="G1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:10">
       <c r="A2" s="2">
         <v>0</v>
       </c>
@@ -476,8 +505,20 @@
       <c r="F2" s="2">
         <v>1</v>
       </c>
+      <c r="G2" s="2">
+        <v>-1</v>
+      </c>
+      <c r="H2" s="2">
+        <v>-1</v>
+      </c>
+      <c r="I2" s="2">
+        <v>-1</v>
+      </c>
+      <c r="J2" s="2">
+        <v>-1</v>
+      </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:10">
       <c r="A3" s="2">
         <v>1</v>
       </c>
@@ -497,8 +538,20 @@
       <c r="F3" s="2">
         <v>1</v>
       </c>
+      <c r="G3" s="2">
+        <v>0</v>
+      </c>
+      <c r="H3" s="2">
+        <v>1</v>
+      </c>
+      <c r="I3" s="2">
+        <v>-1</v>
+      </c>
+      <c r="J3" s="2">
+        <v>-1</v>
+      </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:10">
       <c r="A4" s="2">
         <v>2</v>
       </c>
@@ -518,8 +571,20 @@
       <c r="F4" s="2">
         <v>2</v>
       </c>
+      <c r="G4" s="2">
+        <v>0</v>
+      </c>
+      <c r="H4" s="2">
+        <v>2</v>
+      </c>
+      <c r="I4" s="2">
+        <v>-1</v>
+      </c>
+      <c r="J4" s="2">
+        <v>-1</v>
+      </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:10">
       <c r="A5" s="2">
         <v>3</v>
       </c>
@@ -539,8 +604,20 @@
       <c r="F5" s="2">
         <v>2</v>
       </c>
+      <c r="G5" s="2">
+        <v>0</v>
+      </c>
+      <c r="H5" s="2">
+        <v>-1</v>
+      </c>
+      <c r="I5" s="2">
+        <v>-1</v>
+      </c>
+      <c r="J5" s="2">
+        <v>-1</v>
+      </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:10">
       <c r="A6" s="2">
         <v>4</v>
       </c>
@@ -559,6 +636,18 @@
       </c>
       <c r="F6" s="2">
         <v>1</v>
+      </c>
+      <c r="G6" s="2">
+        <v>0</v>
+      </c>
+      <c r="H6" s="2">
+        <v>-1</v>
+      </c>
+      <c r="I6" s="2">
+        <v>-1</v>
+      </c>
+      <c r="J6" s="2">
+        <v>-1</v>
       </c>
     </row>
   </sheetData>
